--- a/data/processed/green_harmonic_model.xlsx
+++ b/data/processed/green_harmonic_model.xlsx
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>580</v>
+        <v>730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>bom_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>data/processed/bom_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BOM模板候选值；待工程成员核验</t>
+          <t>按 2024 年报谐波减速器及金属件毛利率 36.13% 锚定：1150×(1-36.5%)≈730；修正前 580 元隐含 GM 49.6% 偏乐观</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>560</v>
+        <v>710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1092,17 +1092,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>bom_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>data/processed/bom_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BOM模板候选值；待工程成员核验</t>
+          <t>毛利率口径同上（2026 隐含 GM 约 35.5%）</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>540</v>
+        <v>690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>bom_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>data/processed/bom_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BOM模板候选值；待工程成员核验</t>
+          <t>毛利率口径同上（2027 隐含 GM 约 34.3%，含降价压力）</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1772,17 +1772,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>project_scenario_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>data/processed/financial_model_inputs_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>简化模型假设；实际税率待财务成员核对</t>
+          <t>2024 年报原文：已取得高新技术企业认定，减按 15%税率缴纳所得税；修正前 25% 偏保守</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1812,17 +1812,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>project_scenario_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>data/processed/financial_model_inputs_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>简化模型假设；实际税率待财务成员核对</t>
+          <t>同上（高新资质有效期内 15%）</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1852,17 +1852,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>project_scenario_template</t>
+          <t>green_harmonic_2024_annual_report.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>data/processed/financial_model_inputs_template.csv</t>
+          <t>data/raw/company_filings/green_harmonic_2024_annual_report.pdf.meta.json</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>简化模型假设；实际税率待财务成员核对</t>
+          <t>同上（高新资质有效期内 15%）</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.00560508</v>
+        <v>3.07816411</v>
       </c>
       <c r="C2" t="n">
         <v>4.625</v>
       </c>
       <c r="D2" t="n">
-        <v>0.47025</v>
+        <v>0.243</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.65003424</v>
+        <v>5.85017459</v>
       </c>
       <c r="C3" t="n">
         <v>5.240125</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67799964</v>
+        <v>0.46092375</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.21577278</v>
+        <v>0.09437249</v>
       </c>
       <c r="C4" t="n">
         <v>4.037625</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25105047</v>
+        <v>0.00844752</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.754</v>
+        <v>0.949</v>
       </c>
       <c r="C2" t="n">
-        <v>1.008</v>
+        <v>1.278</v>
       </c>
       <c r="D2" t="n">
-        <v>1.35</v>
+        <v>1.725</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.044</v>
+        <v>1.239</v>
       </c>
       <c r="C9" t="n">
-        <v>1.683</v>
+        <v>1.953</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6</v>
+        <v>2.975</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.931</v>
+        <v>0.736</v>
       </c>
       <c r="C10" t="n">
-        <v>1.397</v>
+        <v>1.127</v>
       </c>
       <c r="D10" t="n">
-        <v>2.025</v>
+        <v>1.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.47139241</v>
+        <v>0.37265823</v>
       </c>
       <c r="C11" t="n">
-        <v>0.45357143</v>
+        <v>0.36590909</v>
       </c>
       <c r="D11" t="n">
-        <v>0.43783784</v>
+        <v>0.35675676</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.51625</v>
+        <v>0.32125</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7502</v>
+        <v>0.4802</v>
       </c>
       <c r="D13" t="n">
-        <v>1.05375</v>
+        <v>0.67875</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.26139241</v>
+        <v>0.16265823</v>
       </c>
       <c r="C14" t="n">
-        <v>0.24357143</v>
+        <v>0.15590909</v>
       </c>
       <c r="D14" t="n">
-        <v>0.22783784</v>
+        <v>0.14675676</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.457</v>
+        <v>0.262</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.3878</v>
       </c>
       <c r="D15" t="n">
-        <v>0.915</v>
+        <v>0.54</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.11425</v>
+        <v>0.0393</v>
       </c>
       <c r="C16" t="n">
-        <v>0.16445</v>
+        <v>0.05817</v>
       </c>
       <c r="D16" t="n">
-        <v>0.22875</v>
+        <v>0.081</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.18475</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3457</v>
+        <v>0.18198</v>
       </c>
       <c r="D19" t="n">
-        <v>0.47025</v>
+        <v>0.243</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.00560508</v>
+        <v>3.07816411</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -2774,13 +2774,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.804518</v>
+        <v>1.012583</v>
       </c>
       <c r="C2" t="n">
-        <v>1.075536</v>
+        <v>1.363626</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44045</v>
+        <v>1.840575</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2921,13 +2921,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.113948</v>
+        <v>1.322013</v>
       </c>
       <c r="C9" t="n">
-        <v>1.795761</v>
+        <v>2.083851</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7742</v>
+        <v>3.174325</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.123727</v>
+        <v>0.915662</v>
       </c>
       <c r="C10" t="n">
-        <v>1.693879</v>
+        <v>1.405789</v>
       </c>
       <c r="D10" t="n">
-        <v>2.465925</v>
+        <v>2.0658</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.50218508</v>
+        <v>0.40920241</v>
       </c>
       <c r="C11" t="n">
-        <v>0.48540222</v>
+        <v>0.40284643</v>
       </c>
       <c r="D11" t="n">
-        <v>0.47058515</v>
+        <v>0.39422724</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.66321348</v>
+        <v>0.45514848</v>
       </c>
       <c r="C13" t="n">
-        <v>0.97571109</v>
+        <v>0.68762109</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38750728</v>
+        <v>0.9873822799999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3026,13 +3026,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.29638508</v>
+        <v>0.20340241</v>
       </c>
       <c r="C14" t="n">
-        <v>0.27960222</v>
+        <v>0.19704643</v>
       </c>
       <c r="D14" t="n">
-        <v>0.26478515</v>
+        <v>0.18842724</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3047,13 +3047,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.59608323</v>
+        <v>0.38801823</v>
       </c>
       <c r="C15" t="n">
-        <v>0.87102189</v>
+        <v>0.58293189</v>
       </c>
       <c r="D15" t="n">
-        <v>1.23030353</v>
+        <v>0.83017853</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.14902081</v>
+        <v>0.05820274</v>
       </c>
       <c r="C16" t="n">
-        <v>0.21775547</v>
+        <v>0.08743977999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.30757588</v>
+        <v>0.12452678</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.26804843</v>
+        <v>0.1508015</v>
       </c>
       <c r="C19" t="n">
-        <v>0.48597897</v>
+        <v>0.32820465</v>
       </c>
       <c r="D19" t="n">
-        <v>0.67799964</v>
+        <v>0.46092375</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.65003424</v>
+        <v>5.85017459</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.71253</v>
+        <v>0.896805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.95256</v>
+        <v>1.20771</v>
       </c>
       <c r="D2" t="n">
-        <v>1.27575</v>
+        <v>1.630125</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.98658</v>
+        <v>1.170855</v>
       </c>
       <c r="C9" t="n">
-        <v>1.590435</v>
+        <v>1.845585</v>
       </c>
       <c r="D9" t="n">
-        <v>2.457</v>
+        <v>2.811375</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.737595</v>
+        <v>0.55332</v>
       </c>
       <c r="C10" t="n">
-        <v>1.098405</v>
+        <v>0.843255</v>
       </c>
       <c r="D10" t="n">
-        <v>1.580625</v>
+        <v>1.22625</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3399,13 +3399,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4277959</v>
+        <v>0.3209187</v>
       </c>
       <c r="C11" t="n">
-        <v>0.40850515</v>
+        <v>0.31361293</v>
       </c>
       <c r="D11" t="n">
-        <v>0.39147395</v>
+        <v>0.30370577</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.36465595</v>
+        <v>0.18038095</v>
       </c>
       <c r="C13" t="n">
-        <v>0.51680891</v>
+        <v>0.26165891</v>
       </c>
       <c r="D13" t="n">
-        <v>0.70728671</v>
+        <v>0.35291171</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2114959</v>
+        <v>0.1046187</v>
       </c>
       <c r="C14" t="n">
-        <v>0.19220515</v>
+        <v>0.09731293000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.17517395</v>
+        <v>0.08740576999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3129307</v>
+        <v>0.1286557</v>
       </c>
       <c r="C15" t="n">
-        <v>0.43614371</v>
+        <v>0.18099371</v>
       </c>
       <c r="D15" t="n">
-        <v>0.58615796</v>
+        <v>0.23178296</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07823267</v>
+        <v>0.01929835</v>
       </c>
       <c r="C16" t="n">
-        <v>0.10903593</v>
+        <v>0.02714906</v>
       </c>
       <c r="D16" t="n">
-        <v>0.14653949</v>
+        <v>0.03476744</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09676402000000001</v>
+        <v>-0.02857666</v>
       </c>
       <c r="C19" t="n">
-        <v>0.19820933</v>
+        <v>0.0249462</v>
       </c>
       <c r="D19" t="n">
-        <v>0.25105047</v>
+        <v>0.00844752</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.21577278</v>
+        <v>0.09437249</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
